--- a/BSA/doc/MultiThread Test.xlsx
+++ b/BSA/doc/MultiThread Test.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4507"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://365andrew-my.sharepoint.com/personal/fengjun_zhang_andrew_com/Documents/Documents/01CATS/01CATS PIM/BSA/doc/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_4900A87B9331D4E301864ED2D115E615557C2DEA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-780" yWindow="3285" windowWidth="20010" windowHeight="7545"/>
+    <workbookView xWindow="8175" yWindow="6075" windowWidth="28800" windowHeight="15345" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="4" r:id="rId1"/>
@@ -12,7 +18,20 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
     <sheet name="Sheet4" sheetId="5" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="125725"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -370,11 +389,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m/d;@"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -761,7 +780,23 @@
       <color rgb="FFFF66FF"/>
     </mruColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp1.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp2.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -781,7 +816,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="TextBox 1"/>
+        <xdr:cNvPr id="2" name="TextBox 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -869,7 +910,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="TextBox 2"/>
+        <xdr:cNvPr id="3" name="TextBox 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -941,7 +988,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="4" name="Shape 3"/>
+        <xdr:cNvPr id="4" name="Shape 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="2" idx="2"/>
           <a:endCxn id="3" idx="1"/>
@@ -997,7 +1050,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="TextBox 4"/>
+        <xdr:cNvPr id="5" name="TextBox 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1074,7 +1133,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="6" name="Straight Arrow Connector 5"/>
+        <xdr:cNvPr id="6" name="Straight Arrow Connector 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000006000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="2" idx="3"/>
           <a:endCxn id="5" idx="1"/>
@@ -1127,7 +1192,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="7" name="TextBox 6"/>
+        <xdr:cNvPr id="7" name="TextBox 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000007000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1275,7 +1346,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="8" name="TextBox 7"/>
+        <xdr:cNvPr id="8" name="TextBox 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000008000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1371,7 +1448,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="9" name="TextBox 8"/>
+        <xdr:cNvPr id="9" name="TextBox 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000009000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1486,7 +1569,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="10" name="TextBox 9"/>
+        <xdr:cNvPr id="10" name="TextBox 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1604,7 +1693,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="11" name="Straight Arrow Connector 10"/>
+        <xdr:cNvPr id="11" name="Straight Arrow Connector 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="10" idx="2"/>
           <a:endCxn id="8" idx="0"/>
@@ -1660,7 +1755,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="12" name="Straight Arrow Connector 11"/>
+        <xdr:cNvPr id="12" name="Straight Arrow Connector 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="3" idx="2"/>
           <a:endCxn id="10" idx="0"/>
@@ -1716,7 +1817,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="13" name="TextBox 12"/>
+        <xdr:cNvPr id="13" name="TextBox 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1834,7 +1941,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="14" name="Straight Arrow Connector 13"/>
+        <xdr:cNvPr id="14" name="Straight Arrow Connector 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -1887,7 +2000,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="15" name="TextBox 14"/>
+        <xdr:cNvPr id="15" name="TextBox 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1983,7 +2102,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="16" name="Straight Arrow Connector 15"/>
+        <xdr:cNvPr id="16" name="Straight Arrow Connector 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000010000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -2036,7 +2161,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="17" name="TextBox 16"/>
+        <xdr:cNvPr id="17" name="TextBox 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000011000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2367,7 +2498,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="18" name="Straight Arrow Connector 17"/>
+        <xdr:cNvPr id="18" name="Straight Arrow Connector 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000012000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -2420,7 +2557,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="19" name="TextBox 18"/>
+        <xdr:cNvPr id="19" name="TextBox 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000013000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2535,7 +2678,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="20" name="Elbow Connector 19"/>
+        <xdr:cNvPr id="20" name="Elbow Connector 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000014000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="15" idx="3"/>
           <a:endCxn id="7" idx="0"/>
@@ -2591,7 +2740,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="21" name="Elbow Connector 20"/>
+        <xdr:cNvPr id="21" name="Elbow Connector 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000015000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="15" idx="3"/>
           <a:endCxn id="9" idx="0"/>
@@ -2647,7 +2802,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="22" name="Elbow Connector 21"/>
+        <xdr:cNvPr id="22" name="Elbow Connector 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000016000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="15" idx="3"/>
           <a:endCxn id="19" idx="0"/>
@@ -2703,7 +2864,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="23" name="Straight Arrow Connector 22"/>
+        <xdr:cNvPr id="23" name="Straight Arrow Connector 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000017000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="15" idx="2"/>
           <a:endCxn id="64" idx="0"/>
@@ -2759,7 +2926,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="24" name="TextBox 23"/>
+        <xdr:cNvPr id="24" name="TextBox 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000018000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2877,7 +3050,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="25" name="TextBox 24"/>
+        <xdr:cNvPr id="25" name="TextBox 24">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000019000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2995,7 +3174,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="26" name="Straight Arrow Connector 25"/>
+        <xdr:cNvPr id="26" name="Straight Arrow Connector 25">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -3048,7 +3233,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="27" name="Straight Arrow Connector 26"/>
+        <xdr:cNvPr id="27" name="Straight Arrow Connector 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -3098,7 +3289,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="28" name="Straight Arrow Connector 27"/>
+        <xdr:cNvPr id="28" name="Straight Arrow Connector 27">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -3148,7 +3345,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="29" name="TextBox 28"/>
+        <xdr:cNvPr id="29" name="TextBox 28">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -3296,7 +3499,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="30" name="TextBox 29"/>
+        <xdr:cNvPr id="30" name="TextBox 29">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -3414,7 +3623,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="31" name="Straight Arrow Connector 30"/>
+        <xdr:cNvPr id="31" name="Straight Arrow Connector 30">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -3464,7 +3679,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="32" name="Straight Arrow Connector 31"/>
+        <xdr:cNvPr id="32" name="Straight Arrow Connector 31">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000020000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="56" idx="2"/>
           <a:endCxn id="30" idx="0"/>
@@ -3517,7 +3738,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="33" name="TextBox 32"/>
+        <xdr:cNvPr id="33" name="TextBox 32">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000021000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -3605,7 +3832,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="34" name="TextBox 33"/>
+        <xdr:cNvPr id="34" name="TextBox 33">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000022000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -3693,7 +3926,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="35" name="TextBox 34"/>
+        <xdr:cNvPr id="35" name="TextBox 34">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000023000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -3811,7 +4050,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="36" name="Straight Arrow Connector 35"/>
+        <xdr:cNvPr id="36" name="Straight Arrow Connector 35">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000024000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -3861,7 +4106,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="37" name="Straight Arrow Connector 36"/>
+        <xdr:cNvPr id="37" name="Straight Arrow Connector 36">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000025000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -3913,7 +4164,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="38" name="Straight Arrow Connector 37"/>
+        <xdr:cNvPr id="38" name="Straight Arrow Connector 37">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000026000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -3965,7 +4222,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="39" name="Straight Arrow Connector 38"/>
+        <xdr:cNvPr id="39" name="Straight Arrow Connector 38">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000027000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -4015,7 +4278,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="40" name="Straight Arrow Connector 39"/>
+        <xdr:cNvPr id="40" name="Straight Arrow Connector 39">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000028000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -4065,7 +4334,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="41" name="TextBox 40"/>
+        <xdr:cNvPr id="41" name="TextBox 40">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000029000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -4130,7 +4405,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="42" name="TextBox 41"/>
+        <xdr:cNvPr id="42" name="TextBox 41">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -4195,7 +4476,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="43" name="TextBox 42"/>
+        <xdr:cNvPr id="43" name="TextBox 42">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -4340,7 +4627,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="45" name="TextBox 44"/>
+        <xdr:cNvPr id="45" name="TextBox 44">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -4482,7 +4775,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="46" name="Straight Arrow Connector 45"/>
+        <xdr:cNvPr id="46" name="Straight Arrow Connector 45">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -4532,7 +4831,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="47" name="TextBox 46"/>
+        <xdr:cNvPr id="47" name="TextBox 46">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -4620,7 +4925,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="48" name="Straight Arrow Connector 47"/>
+        <xdr:cNvPr id="48" name="Straight Arrow Connector 47">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000030000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -4670,7 +4981,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="49" name="TextBox 48"/>
+        <xdr:cNvPr id="49" name="TextBox 48">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000031000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -4758,7 +5075,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="50" name="Straight Arrow Connector 49"/>
+        <xdr:cNvPr id="50" name="Straight Arrow Connector 49">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000032000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -4808,7 +5131,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="51" name="TextBox 50"/>
+        <xdr:cNvPr id="51" name="TextBox 50">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000033000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -4896,7 +5225,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="52" name="Straight Arrow Connector 51"/>
+        <xdr:cNvPr id="52" name="Straight Arrow Connector 51">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000034000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -4946,7 +5281,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="53" name="Straight Arrow Connector 52"/>
+        <xdr:cNvPr id="53" name="Straight Arrow Connector 52">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000035000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="77" idx="2"/>
           <a:endCxn id="24" idx="0"/>
@@ -4999,7 +5340,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="54" name="Straight Arrow Connector 53"/>
+        <xdr:cNvPr id="54" name="Straight Arrow Connector 53">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000036000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -5051,7 +5398,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="55" name="TextBox 54"/>
+        <xdr:cNvPr id="55" name="TextBox 54">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000037000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -5116,7 +5469,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="56" name="TextBox 55"/>
+        <xdr:cNvPr id="56" name="TextBox 55">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000038000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -5258,7 +5617,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="57" name="TextBox 56"/>
+        <xdr:cNvPr id="57" name="TextBox 56">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000039000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -5346,7 +5711,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="58" name="Straight Arrow Connector 57"/>
+        <xdr:cNvPr id="58" name="Straight Arrow Connector 57">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -5396,7 +5767,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="59" name="Straight Arrow Connector 58"/>
+        <xdr:cNvPr id="59" name="Straight Arrow Connector 58">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -5446,7 +5823,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="60" name="Straight Arrow Connector 59"/>
+        <xdr:cNvPr id="60" name="Straight Arrow Connector 59">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -5498,7 +5881,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="61" name="TextBox 60"/>
+        <xdr:cNvPr id="61" name="TextBox 60">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -5563,7 +5952,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="62" name="TextBox 61"/>
+        <xdr:cNvPr id="62" name="TextBox 61">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -5695,7 +6090,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="64" name="TextBox 63"/>
+        <xdr:cNvPr id="64" name="TextBox 63">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000040000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -5786,7 +6187,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="65" name="Straight Arrow Connector 64"/>
+        <xdr:cNvPr id="65" name="Straight Arrow Connector 64">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000041000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -5839,7 +6246,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="66" name="TextBox 65"/>
+        <xdr:cNvPr id="66" name="TextBox 65">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000042000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -5930,7 +6343,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="77" name="TextBox 76"/>
+        <xdr:cNvPr id="77" name="TextBox 76">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -6072,7 +6491,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="78" name="TextBox 77"/>
+        <xdr:cNvPr id="78" name="TextBox 77">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -6225,7 +6650,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="107" name="Straight Arrow Connector 106"/>
+        <xdr:cNvPr id="107" name="Straight Arrow Connector 106">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -6276,7 +6707,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="108" name="Straight Arrow Connector 107"/>
+        <xdr:cNvPr id="108" name="Straight Arrow Connector 107">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="47" idx="2"/>
         </xdr:cNvCxnSpPr>
@@ -6329,7 +6766,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="109" name="Straight Arrow Connector 108"/>
+        <xdr:cNvPr id="109" name="Straight Arrow Connector 108">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="49" idx="2"/>
         </xdr:cNvCxnSpPr>
@@ -6382,7 +6825,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="111" name="TextBox 110"/>
+        <xdr:cNvPr id="111" name="TextBox 110">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -6507,7 +6956,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="114" name="Straight Arrow Connector 113"/>
+        <xdr:cNvPr id="114" name="Straight Arrow Connector 113">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000072000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -6557,7 +7012,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="115" name="Straight Arrow Connector 114"/>
+        <xdr:cNvPr id="115" name="Straight Arrow Connector 114">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000073000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -6607,7 +7068,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="116" name="TextBox 115"/>
+        <xdr:cNvPr id="116" name="TextBox 115">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000074000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -6673,7 +7140,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="117" name="TextBox 116"/>
+        <xdr:cNvPr id="117" name="TextBox 116">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000075000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -6738,7 +7211,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="118" name="Straight Arrow Connector 117"/>
+        <xdr:cNvPr id="118" name="Straight Arrow Connector 117">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000076000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -6788,7 +7267,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="119" name="TextBox 118"/>
+        <xdr:cNvPr id="119" name="TextBox 118">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000077000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -6868,7 +7353,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="120" name="TextBox 119"/>
+        <xdr:cNvPr id="120" name="TextBox 119">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000078000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -6948,7 +7439,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="121" name="Diamond 120"/>
+        <xdr:cNvPr id="121" name="Diamond 120">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000079000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -7069,7 +7566,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="122" name="Straight Arrow Connector 121"/>
+        <xdr:cNvPr id="122" name="Straight Arrow Connector 121">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00007A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -7122,7 +7625,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="123" name="Straight Arrow Connector 122"/>
+        <xdr:cNvPr id="123" name="Straight Arrow Connector 122">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00007B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -7172,7 +7681,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="125" name="TextBox 124"/>
+        <xdr:cNvPr id="125" name="TextBox 124">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00007D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -7237,7 +7752,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="130" name="TextBox 129"/>
+        <xdr:cNvPr id="130" name="TextBox 129">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000082000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -7451,7 +7972,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="131" name="TextBox 130"/>
+        <xdr:cNvPr id="131" name="TextBox 130">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000083000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -7681,7 +8208,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="132" name="TextBox 131"/>
+        <xdr:cNvPr id="132" name="TextBox 131">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000084000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -7968,7 +8501,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="153" name="TextBox 152"/>
+        <xdr:cNvPr id="153" name="TextBox 152">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000099000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -8293,7 +8832,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="154" name="TextBox 153"/>
+        <xdr:cNvPr id="154" name="TextBox 153">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00009A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -8361,7 +8906,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="155" name="TextBox 154"/>
+        <xdr:cNvPr id="155" name="TextBox 154">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00009B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -8459,7 +9010,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="162" name="TextBox 161"/>
+        <xdr:cNvPr id="162" name="TextBox 161">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000A2000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -8527,7 +9084,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="163" name="TextBox 162"/>
+        <xdr:cNvPr id="163" name="TextBox 162">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000A3000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -8595,7 +9158,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="164" name="TextBox 163"/>
+        <xdr:cNvPr id="164" name="TextBox 163">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000A4000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -8677,7 +9246,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="165" name="TextBox 164"/>
+        <xdr:cNvPr id="165" name="TextBox 164">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000A5000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -8747,7 +9322,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="167" name="TextBox 166"/>
+        <xdr:cNvPr id="167" name="TextBox 166">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000A7000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -8817,7 +9398,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="168" name="Straight Arrow Connector 167"/>
+        <xdr:cNvPr id="168" name="Straight Arrow Connector 167">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000A8000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -8867,7 +9454,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="171" name="TextBox 170"/>
+        <xdr:cNvPr id="171" name="TextBox 170">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000AB000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -8932,7 +9525,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="195" name="Straight Arrow Connector 194"/>
+        <xdr:cNvPr id="195" name="Straight Arrow Connector 194">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000C3000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="165" idx="2"/>
         </xdr:cNvCxnSpPr>
@@ -8984,7 +9583,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="200" name="Shape 199"/>
+        <xdr:cNvPr id="200" name="Shape 199">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000C8000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="164" idx="3"/>
           <a:endCxn id="165" idx="0"/>
@@ -9037,7 +9642,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="202" name="Shape 201"/>
+        <xdr:cNvPr id="202" name="Shape 201">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000CA000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="154" idx="3"/>
           <a:endCxn id="155" idx="0"/>
@@ -9090,7 +9701,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="177" name="TextBox 176"/>
+        <xdr:cNvPr id="177" name="TextBox 176">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000B1000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -9160,7 +9777,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="199" name="Diamond 198"/>
+        <xdr:cNvPr id="199" name="Diamond 198">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000C7000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -9310,7 +9933,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="203" name="Shape 202"/>
+        <xdr:cNvPr id="203" name="Shape 202">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000CB000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="199" idx="1"/>
           <a:endCxn id="153" idx="0"/>
@@ -9366,7 +9995,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="204" name="TextBox 203"/>
+        <xdr:cNvPr id="204" name="TextBox 203">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000CC000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -9439,7 +10074,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="211" name="Diamond 210"/>
+        <xdr:cNvPr id="211" name="Diamond 210">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000D3000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -9522,7 +10163,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="213" name="Straight Arrow Connector 212"/>
+        <xdr:cNvPr id="213" name="Straight Arrow Connector 212">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000D5000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="199" idx="2"/>
           <a:endCxn id="211" idx="0"/>
@@ -9578,7 +10225,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="215" name="Straight Arrow Connector 214"/>
+        <xdr:cNvPr id="215" name="Straight Arrow Connector 214">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000D7000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="211" idx="2"/>
           <a:endCxn id="62" idx="0"/>
@@ -9634,7 +10287,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="216" name="TextBox 215"/>
+        <xdr:cNvPr id="216" name="TextBox 215">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000D8000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -9707,7 +10366,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="219" name="Straight Arrow Connector 218"/>
+        <xdr:cNvPr id="219" name="Straight Arrow Connector 218">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000DB000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="62" idx="2"/>
           <a:endCxn id="111" idx="0"/>
@@ -9763,7 +10428,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="223" name="Straight Arrow Connector 222"/>
+        <xdr:cNvPr id="223" name="Straight Arrow Connector 222">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000DF000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="111" idx="2"/>
           <a:endCxn id="121" idx="0"/>
@@ -9819,7 +10490,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="237" name="TextBox 236"/>
+        <xdr:cNvPr id="237" name="TextBox 236">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000ED000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -9973,7 +10650,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="241" name="Straight Arrow Connector 240"/>
+        <xdr:cNvPr id="241" name="Straight Arrow Connector 240">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000F1000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="153" idx="2"/>
           <a:endCxn id="237" idx="0"/>
@@ -10029,7 +10712,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="243" name="Elbow Connector 242"/>
+        <xdr:cNvPr id="243" name="Elbow Connector 242">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000F3000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="237" idx="2"/>
           <a:endCxn id="121" idx="1"/>
@@ -10085,7 +10774,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="252" name="Diamond 251"/>
+        <xdr:cNvPr id="252" name="Diamond 251">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000FC000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -10248,7 +10943,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="255" name="Straight Arrow Connector 254"/>
+        <xdr:cNvPr id="255" name="Straight Arrow Connector 254">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000FF000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="252" idx="2"/>
           <a:endCxn id="29" idx="0"/>
@@ -10304,7 +11005,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="257" name="Straight Arrow Connector 256"/>
+        <xdr:cNvPr id="257" name="Straight Arrow Connector 256">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001010000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="29" idx="2"/>
           <a:endCxn id="43" idx="0"/>
@@ -10360,7 +11067,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="258" name="TextBox 257"/>
+        <xdr:cNvPr id="258" name="TextBox 257">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002010000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -10433,7 +11146,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="265" name="Diamond 264"/>
+        <xdr:cNvPr id="265" name="Diamond 264">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000009010000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -10511,7 +11230,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="270" name="Shape 269"/>
+        <xdr:cNvPr id="270" name="Shape 269">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000E010000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="265" idx="1"/>
         </xdr:cNvCxnSpPr>
@@ -10563,7 +11288,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="271" name="TextBox 270"/>
+        <xdr:cNvPr id="271" name="TextBox 270">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000F010000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -10647,7 +11378,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="273" name="Straight Arrow Connector 272"/>
+        <xdr:cNvPr id="273" name="Straight Arrow Connector 272">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000011010000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="265" idx="2"/>
           <a:endCxn id="177" idx="0"/>
@@ -10700,7 +11437,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="275" name="TextBox 274"/>
+        <xdr:cNvPr id="275" name="TextBox 274">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000013010000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -10765,7 +11508,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="276" name="TextBox 275"/>
+        <xdr:cNvPr id="276" name="TextBox 275">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000014010000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -10843,7 +11592,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="278" name="Straight Arrow Connector 277"/>
+        <xdr:cNvPr id="278" name="Straight Arrow Connector 277">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000016010000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="177" idx="2"/>
           <a:endCxn id="276" idx="0"/>
@@ -10896,7 +11651,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="280" name="Shape 279"/>
+        <xdr:cNvPr id="280" name="Shape 279">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000018010000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:endCxn id="276" idx="1"/>
         </xdr:cNvCxnSpPr>
@@ -10948,7 +11709,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="281" name="Diamond 280"/>
+        <xdr:cNvPr id="281" name="Diamond 280">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000019010000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -11026,7 +11793,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="283" name="Straight Arrow Connector 282"/>
+        <xdr:cNvPr id="283" name="Straight Arrow Connector 282">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001B010000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="276" idx="2"/>
           <a:endCxn id="281" idx="0"/>
@@ -11079,7 +11852,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="285" name="Elbow Connector 284"/>
+        <xdr:cNvPr id="285" name="Elbow Connector 284">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001D010000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="281" idx="3"/>
           <a:endCxn id="165" idx="3"/>
@@ -11134,7 +11913,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="287" name="TextBox 286"/>
+        <xdr:cNvPr id="287" name="TextBox 286">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001F010000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -11199,7 +11984,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="288" name="TextBox 287"/>
+        <xdr:cNvPr id="288" name="TextBox 287">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000020010000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -11269,7 +12060,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="290" name="TextBox 289"/>
+        <xdr:cNvPr id="290" name="TextBox 289">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000022010000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -11351,7 +12148,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="296" name="TextBox 295"/>
+        <xdr:cNvPr id="296" name="TextBox 295">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000028010000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -11416,7 +12219,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="297" name="TextBox 296"/>
+        <xdr:cNvPr id="297" name="TextBox 296">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000029010000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -11498,7 +12307,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="298" name="Straight Arrow Connector 297"/>
+        <xdr:cNvPr id="298" name="Straight Arrow Connector 297">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002A010000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -11533,6 +12348,180 @@
     </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>104775</xdr:colOff>
+          <xdr:row>17</xdr:row>
+          <xdr:rowOff>9525</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>104775</xdr:colOff>
+          <xdr:row>18</xdr:row>
+          <xdr:rowOff>57150</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="2049" name="Check Box 1" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s2049"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FEA06E68-48B2-9A16-E726-EEEE163384A3}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Tahoma"/>
+                  <a:ea typeface="Tahoma"/>
+                  <a:cs typeface="Tahoma"/>
+                </a:rPr>
+                <a:t>PIM1800</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>104775</xdr:colOff>
+          <xdr:row>15</xdr:row>
+          <xdr:rowOff>95250</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>104775</xdr:colOff>
+          <xdr:row>16</xdr:row>
+          <xdr:rowOff>142875</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="2050" name="Check Box 2" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s2050"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F13A1C97-8692-2639-FA3D-61B0A003AB09}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Tahoma"/>
+                  <a:ea typeface="Tahoma"/>
+                  <a:cs typeface="Tahoma"/>
+                </a:rPr>
+                <a:t>PIM700</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
 </xdr:wsDr>
 </file>
 
@@ -11553,7 +12542,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="2" name="Straight Arrow Connector 1"/>
+        <xdr:cNvPr id="2" name="Straight Arrow Connector 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -11603,7 +12598,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="4" name="Straight Arrow Connector 3"/>
+        <xdr:cNvPr id="4" name="Straight Arrow Connector 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -11653,7 +12654,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="6" name="Straight Arrow Connector 5"/>
+        <xdr:cNvPr id="6" name="Straight Arrow Connector 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000006000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -11703,7 +12710,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="7" name="Straight Arrow Connector 6"/>
+        <xdr:cNvPr id="7" name="Straight Arrow Connector 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000007000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -11753,7 +12766,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="9" name="Straight Arrow Connector 8"/>
+        <xdr:cNvPr id="9" name="Straight Arrow Connector 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000009000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -11803,7 +12822,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="11" name="Straight Arrow Connector 10"/>
+        <xdr:cNvPr id="11" name="Straight Arrow Connector 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -11853,7 +12878,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="12" name="Straight Arrow Connector 11"/>
+        <xdr:cNvPr id="12" name="Straight Arrow Connector 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -11903,7 +12934,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="14" name="Straight Arrow Connector 13"/>
+        <xdr:cNvPr id="14" name="Straight Arrow Connector 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -11953,7 +12990,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="15" name="Straight Arrow Connector 14"/>
+        <xdr:cNvPr id="15" name="Straight Arrow Connector 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -12003,7 +13046,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="16" name="Straight Arrow Connector 15"/>
+        <xdr:cNvPr id="16" name="Straight Arrow Connector 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000010000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -12053,7 +13102,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="17" name="Straight Arrow Connector 16"/>
+        <xdr:cNvPr id="17" name="Straight Arrow Connector 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000011000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -12103,7 +13158,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="25" name="Straight Connector 24"/>
+        <xdr:cNvPr id="25" name="Straight Connector 24">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000019000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -12147,7 +13208,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="27" name="Straight Connector 26"/>
+        <xdr:cNvPr id="27" name="Straight Connector 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00001B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -12191,7 +13258,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="29" name="Straight Arrow Connector 28"/>
+        <xdr:cNvPr id="29" name="Straight Arrow Connector 28">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00001D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -12238,7 +13311,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="37" name="Straight Arrow Connector 36"/>
+        <xdr:cNvPr id="37" name="Straight Arrow Connector 36">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000025000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -12288,7 +13367,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="40" name="Straight Arrow Connector 39"/>
+        <xdr:cNvPr id="40" name="Straight Arrow Connector 39">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000028000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -12338,7 +13423,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="45" name="Straight Arrow Connector 44"/>
+        <xdr:cNvPr id="45" name="Straight Arrow Connector 44">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00002D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -12377,9 +13468,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -12417,7 +13508,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -12451,6 +13542,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -12485,9 +13577,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -12660,16 +13753,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="C3:T51"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="19" width="9.140625" style="3"/>
     <col min="20" max="20" width="9.140625" style="3" customWidth="1"/>
     <col min="21" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:12">
+    <row r="3" spans="3:12" x14ac:dyDescent="0.3">
       <c r="D3" s="1"/>
       <c r="E3" s="2" t="s">
         <v>0</v>
@@ -12696,7 +13789,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="3:12" ht="16.5" customHeight="1">
+    <row r="4" spans="3:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D4" s="38" t="s">
         <v>8</v>
       </c>
@@ -12715,7 +13808,7 @@
       <c r="K4" s="41"/>
       <c r="L4" s="40"/>
     </row>
-    <row r="5" spans="3:12">
+    <row r="5" spans="3:12" x14ac:dyDescent="0.3">
       <c r="D5" s="38"/>
       <c r="E5" s="42">
         <v>700</v>
@@ -12730,7 +13823,7 @@
       <c r="K5" s="43"/>
       <c r="L5" s="44"/>
     </row>
-    <row r="6" spans="3:12">
+    <row r="6" spans="3:12" x14ac:dyDescent="0.3">
       <c r="D6" s="38"/>
       <c r="E6" s="42">
         <v>900</v>
@@ -12745,7 +13838,7 @@
       <c r="K6" s="43"/>
       <c r="L6" s="44"/>
     </row>
-    <row r="11" spans="3:12">
+    <row r="11" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C11" s="3" t="s">
         <v>9</v>
       </c>
@@ -12760,7 +13853,7 @@
       <c r="J11" s="37"/>
       <c r="K11" s="37"/>
     </row>
-    <row r="12" spans="3:12">
+    <row r="12" spans="3:12" x14ac:dyDescent="0.3">
       <c r="D12" s="37"/>
       <c r="E12" s="37"/>
       <c r="F12" s="37"/>
@@ -12770,7 +13863,7 @@
       <c r="J12" s="37"/>
       <c r="K12" s="37"/>
     </row>
-    <row r="13" spans="3:12">
+    <row r="13" spans="3:12" x14ac:dyDescent="0.3">
       <c r="D13" s="37"/>
       <c r="E13" s="37"/>
       <c r="F13" s="37"/>
@@ -12780,15 +13873,15 @@
       <c r="J13" s="37"/>
       <c r="K13" s="37"/>
     </row>
-    <row r="24" spans="15:16">
+    <row r="24" spans="15:16" x14ac:dyDescent="0.3">
       <c r="O24" s="5"/>
       <c r="P24" s="4"/>
     </row>
-    <row r="25" spans="15:16">
+    <row r="25" spans="15:16" x14ac:dyDescent="0.3">
       <c r="O25" s="5"/>
       <c r="P25" s="4"/>
     </row>
-    <row r="51" spans="20:20">
+    <row r="51" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T51" s="6"/>
     </row>
   </sheetData>
@@ -12809,13 +13902,63 @@
   <pageSetup orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
   <legacyDrawing r:id="rId3"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x14">
+      <controls>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="2049" r:id="rId4" name="Check Box 1">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>2</xdr:col>
+                    <xdr:colOff>104775</xdr:colOff>
+                    <xdr:row>17</xdr:row>
+                    <xdr:rowOff>9525</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>104775</xdr:colOff>
+                    <xdr:row>18</xdr:row>
+                    <xdr:rowOff>57150</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="2050" r:id="rId5" name="Check Box 2">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>2</xdr:col>
+                    <xdr:colOff>104775</xdr:colOff>
+                    <xdr:row>15</xdr:row>
+                    <xdr:rowOff>95250</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>104775</xdr:colOff>
+                    <xdr:row>16</xdr:row>
+                    <xdr:rowOff>142875</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+      </controls>
+    </mc:Choice>
+  </mc:AlternateContent>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="C2:AE59"/>
-  <sheetFormatPr defaultRowHeight="11.25"/>
+  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="9.140625" style="21"/>
     <col min="3" max="3" width="10.7109375" style="21" bestFit="1" customWidth="1"/>
@@ -12837,7 +13980,7 @@
     <col min="29" max="16384" width="9.140625" style="21"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:31">
+    <row r="2" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C2" s="23" t="s">
         <v>16</v>
       </c>
@@ -12845,7 +13988,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="3:31">
+    <row r="3" spans="3:31" x14ac:dyDescent="0.2">
       <c r="I3" s="21" t="s">
         <v>62</v>
       </c>
@@ -12862,7 +14005,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="3:31">
+    <row r="4" spans="3:31" x14ac:dyDescent="0.2">
       <c r="D4" s="21" t="s">
         <v>14</v>
       </c>
@@ -12888,7 +14031,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="3:31">
+    <row r="5" spans="3:31" x14ac:dyDescent="0.2">
       <c r="D5" s="22" t="s">
         <v>37</v>
       </c>
@@ -12911,7 +14054,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="3:31">
+    <row r="6" spans="3:31" x14ac:dyDescent="0.2">
       <c r="D6" s="22" t="s">
         <v>36</v>
       </c>
@@ -12928,7 +14071,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="3:31">
+    <row r="7" spans="3:31" x14ac:dyDescent="0.2">
       <c r="O7" s="21">
         <v>4</v>
       </c>
@@ -12951,7 +14094,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="3:31">
+    <row r="8" spans="3:31" x14ac:dyDescent="0.2">
       <c r="O8" s="21">
         <v>5</v>
       </c>
@@ -12968,7 +14111,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="3:31">
+    <row r="9" spans="3:31" x14ac:dyDescent="0.2">
       <c r="O9" s="21">
         <v>6</v>
       </c>
@@ -12985,7 +14128,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="3:31">
+    <row r="10" spans="3:31" x14ac:dyDescent="0.2">
       <c r="D10" s="21" t="s">
         <v>83</v>
       </c>
@@ -13005,7 +14148,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="11" spans="3:31">
+    <row r="11" spans="3:31" x14ac:dyDescent="0.2">
       <c r="F11" s="21" t="s">
         <v>114</v>
       </c>
@@ -13025,7 +14168,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="12" spans="3:31">
+    <row r="12" spans="3:31" x14ac:dyDescent="0.2">
       <c r="F12" s="21" t="s">
         <v>113</v>
       </c>
@@ -13040,7 +14183,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="3:31">
+    <row r="13" spans="3:31" x14ac:dyDescent="0.2">
       <c r="D13" s="21" t="s">
         <v>59</v>
       </c>
@@ -13052,7 +14195,7 @@
       </c>
       <c r="Q13" s="45"/>
     </row>
-    <row r="14" spans="3:31">
+    <row r="14" spans="3:31" x14ac:dyDescent="0.2">
       <c r="F14" s="35" t="s">
         <v>112</v>
       </c>
@@ -13069,7 +14212,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="3:31">
+    <row r="15" spans="3:31" x14ac:dyDescent="0.2">
       <c r="V15" s="21" t="s">
         <v>17</v>
       </c>
@@ -13086,7 +14229,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="16" spans="3:31">
+    <row r="16" spans="3:31" x14ac:dyDescent="0.2">
       <c r="D16" s="21" t="s">
         <v>54</v>
       </c>
@@ -13094,7 +14237,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="17" spans="4:10">
+    <row r="17" spans="4:10" x14ac:dyDescent="0.2">
       <c r="D17" s="26" t="s">
         <v>81</v>
       </c>
@@ -13103,46 +14246,46 @@
       </c>
       <c r="J17" s="28"/>
     </row>
-    <row r="18" spans="4:10">
+    <row r="18" spans="4:10" x14ac:dyDescent="0.2">
       <c r="I18" s="29" t="s">
         <v>85</v>
       </c>
       <c r="J18" s="30"/>
     </row>
-    <row r="19" spans="4:10">
+    <row r="19" spans="4:10" x14ac:dyDescent="0.2">
       <c r="I19" s="29" t="s">
         <v>86</v>
       </c>
       <c r="J19" s="30"/>
     </row>
-    <row r="20" spans="4:10">
+    <row r="20" spans="4:10" x14ac:dyDescent="0.2">
       <c r="I20" s="29" t="s">
         <v>87</v>
       </c>
       <c r="J20" s="30"/>
     </row>
-    <row r="21" spans="4:10">
+    <row r="21" spans="4:10" x14ac:dyDescent="0.2">
       <c r="I21" s="31" t="s">
         <v>97</v>
       </c>
       <c r="J21" s="32"/>
     </row>
-    <row r="22" spans="4:10">
+    <row r="22" spans="4:10" x14ac:dyDescent="0.2">
       <c r="D22" s="21" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="23" spans="4:10">
+    <row r="23" spans="4:10" x14ac:dyDescent="0.2">
       <c r="D23" s="21" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="26" spans="4:10">
+    <row r="26" spans="4:10" x14ac:dyDescent="0.2">
       <c r="I26" s="21" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="27" spans="4:10">
+    <row r="27" spans="4:10" x14ac:dyDescent="0.2">
       <c r="D27" s="21" t="s">
         <v>57</v>
       </c>
@@ -13156,7 +14299,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="28" spans="4:10">
+    <row r="28" spans="4:10" x14ac:dyDescent="0.2">
       <c r="F28" s="21" t="s">
         <v>114</v>
       </c>
@@ -13164,7 +14307,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="29" spans="4:10">
+    <row r="29" spans="4:10" x14ac:dyDescent="0.2">
       <c r="D29" s="21" t="s">
         <v>58</v>
       </c>
@@ -13175,7 +14318,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="30" spans="4:10">
+    <row r="30" spans="4:10" x14ac:dyDescent="0.2">
       <c r="F30" s="24" t="s">
         <v>61</v>
       </c>
@@ -13183,77 +14326,77 @@
         <v>97</v>
       </c>
     </row>
-    <row r="32" spans="4:10">
+    <row r="32" spans="4:10" x14ac:dyDescent="0.2">
       <c r="D32" s="21" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="33" spans="4:4">
+    <row r="33" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D33" s="21" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="37" spans="4:4">
+    <row r="37" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D37" s="21" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="41" spans="4:4">
+    <row r="41" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D41" s="21" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="42" spans="4:4">
+    <row r="42" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D42" s="21" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="45" spans="4:4">
+    <row r="45" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D45" s="21" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="48" spans="4:4">
+    <row r="48" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D48" s="21" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="50" spans="4:5">
+    <row r="50" spans="4:5" x14ac:dyDescent="0.2">
       <c r="D50" s="34"/>
     </row>
-    <row r="51" spans="4:5">
+    <row r="51" spans="4:5" x14ac:dyDescent="0.2">
       <c r="D51" s="34"/>
     </row>
-    <row r="52" spans="4:5">
+    <row r="52" spans="4:5" x14ac:dyDescent="0.2">
       <c r="D52" s="34" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="53" spans="4:5">
+    <row r="53" spans="4:5" x14ac:dyDescent="0.2">
       <c r="D53" s="34" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="54" spans="4:5">
+    <row r="54" spans="4:5" x14ac:dyDescent="0.2">
       <c r="D54" s="33" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="55" spans="4:5">
+    <row r="55" spans="4:5" x14ac:dyDescent="0.2">
       <c r="D55" s="34"/>
       <c r="E55" s="21" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="56" spans="4:5">
+    <row r="56" spans="4:5" x14ac:dyDescent="0.2">
       <c r="D56" s="21" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="57" spans="4:5">
+    <row r="57" spans="4:5" x14ac:dyDescent="0.2">
       <c r="D57" s="33"/>
     </row>
-    <row r="59" spans="4:5">
+    <row r="59" spans="4:5" x14ac:dyDescent="0.2">
       <c r="E59" s="21" t="s">
         <v>111</v>
       </c>
@@ -13268,9 +14411,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A3:AK13"/>
-  <sheetFormatPr defaultRowHeight="12"/>
+  <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="9"/>
     <col min="2" max="2" width="11.28515625" style="10" bestFit="1" customWidth="1"/>
@@ -13288,7 +14431,7 @@
     <col min="38" max="16384" width="9.140625" style="7"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:37" s="8" customFormat="1">
+    <row r="3" spans="1:37" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="11"/>
       <c r="B3" s="12"/>
       <c r="C3" s="13">
@@ -13397,7 +14540,7 @@
         <v>42855</v>
       </c>
     </row>
-    <row r="4" spans="1:37">
+    <row r="4" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A4" s="14"/>
       <c r="B4" s="15"/>
       <c r="C4" s="16" t="s">
@@ -13506,7 +14649,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:37">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="14">
         <v>1</v>
       </c>
@@ -13549,7 +14692,7 @@
       <c r="AJ5" s="18"/>
       <c r="AK5" s="18"/>
     </row>
-    <row r="6" spans="1:37">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A6" s="14">
         <v>2</v>
       </c>
@@ -13592,7 +14735,7 @@
       <c r="AJ6" s="18"/>
       <c r="AK6" s="18"/>
     </row>
-    <row r="7" spans="1:37">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A7" s="14">
         <v>3</v>
       </c>
@@ -13635,7 +14778,7 @@
       <c r="AJ7" s="18"/>
       <c r="AK7" s="18"/>
     </row>
-    <row r="8" spans="1:37">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A8" s="14">
         <v>4</v>
       </c>
@@ -13678,7 +14821,7 @@
       <c r="AJ8" s="18"/>
       <c r="AK8" s="18"/>
     </row>
-    <row r="9" spans="1:37">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A9" s="14">
         <v>5</v>
       </c>
@@ -13721,7 +14864,7 @@
       <c r="AJ9" s="18"/>
       <c r="AK9" s="18"/>
     </row>
-    <row r="10" spans="1:37">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A10" s="14">
         <v>6</v>
       </c>
@@ -13764,7 +14907,7 @@
       <c r="AJ10" s="18"/>
       <c r="AK10" s="18"/>
     </row>
-    <row r="11" spans="1:37">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A11" s="14">
         <v>7</v>
       </c>
@@ -13807,7 +14950,7 @@
       <c r="AJ11" s="18"/>
       <c r="AK11" s="18"/>
     </row>
-    <row r="12" spans="1:37">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A12" s="14">
         <v>8</v>
       </c>
@@ -13850,7 +14993,7 @@
       <c r="AJ12" s="18"/>
       <c r="AK12" s="18"/>
     </row>
-    <row r="13" spans="1:37">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A13" s="14"/>
       <c r="B13" s="15"/>
       <c r="C13" s="18"/>
@@ -13895,20 +15038,20 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="F9:J11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="9" spans="6:10">
+    <row r="9" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F9">
         <v>2100000000</v>
       </c>
     </row>
-    <row r="11" spans="6:10">
+    <row r="11" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F11">
         <v>5000</v>
       </c>
